--- a/output/pdf_financials_xlsx/FTRC.xlsx
+++ b/output/pdf_financials_xlsx/FTRC.xlsx
@@ -1062,19 +1062,19 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.01128</v>
+        <v>-0.01128</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.362493</v>
+        <v>-0.362493</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.018839</v>
+        <v>-0.018839</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.107948</v>
+        <v>-0.107948</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.040845</v>
+        <v>-0.040845</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>-2.055275</v>
@@ -1274,19 +1274,19 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.01128</v>
+        <v>-0.01128</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.362493</v>
+        <v>-0.362493</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.018839</v>
+        <v>-0.018839</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.107948</v>
+        <v>-0.107948</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.040845</v>
+        <v>-0.040845</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>-2.055275</v>
@@ -1406,19 +1406,19 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.01128</v>
+        <v>-0.01128</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.362493</v>
+        <v>-0.362493</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.018839</v>
+        <v>-0.018839</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.107948</v>
+        <v>-0.107948</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.040845</v>
+        <v>-0.040845</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>-2.055275</v>
@@ -1538,10 +1538,10 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-0.5639999999999999</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-4.531162</v>
+        <v>4.531162</v>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-3.598267</v>
+        <v>3.598267</v>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
@@ -1586,19 +1586,19 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.01128</v>
+        <v>-0.01128</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.362493</v>
+        <v>-0.362493</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.018839</v>
+        <v>-0.018839</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.107948</v>
+        <v>-0.107948</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.040845</v>
+        <v>-0.040845</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-2.055275</v>
@@ -1674,19 +1674,19 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.01128</v>
+        <v>-0.01128</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.362493</v>
+        <v>-0.362493</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.018839</v>
+        <v>-0.018839</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.107948</v>
+        <v>-0.107948</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.040845</v>
+        <v>-0.040845</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-2.054397</v>
@@ -1772,19 +1772,19 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>-0</v>
@@ -4508,16 +4508,16 @@
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.1145</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.1145</v>
       </c>
       <c r="H92" s="3" t="n">
         <v>0.677295</v>
@@ -10413,7 +10413,11 @@
           <t>Share-based payments reserve (note 5)</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -11166,7 +11170,11 @@
           <t>Warrant reserve (note 5)</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -11797,7 +11805,11 @@
           <t>Share-based payments reserve (note 4)</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -11866,7 +11878,11 @@
           <t>Warrants reserve (note 4)</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -25005,10 +25021,10 @@
         </is>
       </c>
       <c r="J265" s="5" t="n">
-        <v>0.040845</v>
+        <v>-0.040845</v>
       </c>
       <c r="K265" s="5" t="n">
-        <v>0.096119</v>
+        <v>-0.096119</v>
       </c>
       <c r="L265" t="inlineStr">
         <is>
@@ -25271,19 +25287,19 @@
         </is>
       </c>
       <c r="F269" s="5" t="n">
-        <v>0.01128</v>
+        <v>-0.01128</v>
       </c>
       <c r="G269" s="5" t="n">
-        <v>0.362493</v>
+        <v>-0.362493</v>
       </c>
       <c r="H269" s="5" t="n">
-        <v>0.018839</v>
+        <v>-0.018839</v>
       </c>
       <c r="I269" s="5" t="n">
-        <v>0.107948</v>
+        <v>-0.107948</v>
       </c>
       <c r="J269" s="5" t="n">
-        <v>0.040845</v>
+        <v>-0.040845</v>
       </c>
       <c r="K269" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/FTRC.xlsx
+++ b/output/pdf_financials_xlsx/FTRC.xlsx
@@ -1877,31 +1877,31 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.364464</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.474505</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.404076</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.29666</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.121153</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.310511</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.803146</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.692124</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.7195820000000001</v>
       </c>
       <c r="L34" s="1" t="inlineStr">
         <is>
@@ -1965,31 +1965,31 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.364464</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.474505</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.404076</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.29666</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.121153</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.310511</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.803146</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.692124</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.7195820000000001</v>
       </c>
       <c r="L36" s="1" t="inlineStr">
         <is>
@@ -2493,31 +2493,31 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.37664</v>
+        <v>0.012176</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.515496</v>
+        <v>0.040991</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.408315</v>
+        <v>0.004239</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.304161</v>
+        <v>0.007501</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.105772</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.565863</v>
+        <v>0.255352</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.130197</v>
+        <v>0.327051</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.1742</v>
+        <v>0.482076</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>2.446654</v>
+        <v>1.727072</v>
       </c>
       <c r="L48" s="1" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -9595,7 +9595,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -21279,7 +21279,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -24018,7 +24018,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">

--- a/output/pdf_financials_xlsx/FTRC.xlsx
+++ b/output/pdf_financials_xlsx/FTRC.xlsx
@@ -14625,7 +14625,11 @@
           <t>Addition to intangible assets</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/FTRC.xlsx
+++ b/output/pdf_financials_xlsx/FTRC.xlsx
@@ -4890,7 +4890,7 @@
         <v>-0.200485</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0.092684</v>
+        <v>0.014856</v>
       </c>
       <c r="J101" s="3" t="n">
         <v>0.479267</v>
@@ -5108,7 +5108,7 @@
         <v>0.047106</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0.345985</v>
+        <v>0.268157</v>
       </c>
       <c r="J106" s="3" t="n">
         <v>2.975408</v>
@@ -5279,16 +5279,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.100313</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.0226</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.133868</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.116106</v>
       </c>
       <c r="L110" s="1" t="inlineStr">
         <is>
@@ -5659,10 +5659,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C119" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D119" s="1" t="inlineStr">
         <is>
@@ -6397,10 +6395,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C135" s="3" t="n">
+        <v>-0.008925000000000001</v>
       </c>
       <c r="D135" s="1" t="inlineStr">
         <is>
@@ -6451,7 +6447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O279"/>
+  <dimension ref="A1:O286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13872,7 +13868,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -16879,7 +16879,11 @@
           <t>HST receivable</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>
@@ -17234,7 +17238,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
@@ -19947,17 +19955,17 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Bank processing fees 13</t>
+          <t>Increase in sales tax recoverable</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
@@ -19966,10 +19974,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F193" s="5" t="n">
+        <v>-0.012176</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
@@ -20001,11 +20007,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M193" s="5" t="n">
-        <v>3.109351</v>
-      </c>
-      <c r="N193" s="5" t="n">
-        <v>3.418336</v>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O193" t="inlineStr">
         <is>
@@ -20016,29 +20026,31 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Enrollment fees 9,13</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr"/>
+          <t>Increase in accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F194" s="5" t="n">
+        <v>0.014531</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
@@ -20070,11 +20082,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M194" s="5" t="n">
-        <v>2.511875</v>
-      </c>
-      <c r="N194" s="5" t="n">
-        <v>2.072536</v>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O194" t="inlineStr">
         <is>
@@ -20085,29 +20101,31 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Education 13</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr"/>
+          <t>Operating activities total</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F195" s="5" t="n">
+        <v>-0.008925000000000001</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
@@ -20144,8 +20162,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N195" s="5" t="n">
-        <v>0.013704</v>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O195" t="inlineStr">
         <is>
@@ -20156,29 +20176,31 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Licensing fees 13</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr"/>
+          <t>Increase in deferred share issuance costs</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F196" s="5" t="n">
+        <v>-0.090361</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
@@ -20215,8 +20237,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N196" s="5" t="n">
-        <v>1.69444</v>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O196" t="inlineStr">
         <is>
@@ -20227,29 +20251,31 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Other revenue 11(c), 13</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr"/>
+          <t>Cash – End of period</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F197" s="5" t="n">
+        <v>0.364464</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
@@ -20281,11 +20307,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M197" s="5" t="n">
-        <v>0.288146</v>
-      </c>
-      <c r="N197" s="5" t="n">
-        <v>0.188327</v>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O197" t="inlineStr">
         <is>
@@ -20306,14 +20336,10 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Total revenue</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
+          <t>Bank processing fees 13</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
@@ -20344,17 +20370,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K198" s="5" t="n">
-        <v>4.369347</v>
-      </c>
-      <c r="L198" s="5" t="n">
-        <v>5.342765</v>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M198" s="5" t="n">
-        <v>5.909372</v>
+        <v>3.109351</v>
       </c>
       <c r="N198" s="5" t="n">
-        <v>7.387343</v>
+        <v>3.418336</v>
       </c>
       <c r="O198" t="inlineStr">
         <is>
@@ -20375,14 +20405,10 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Cost of sales</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>CostOfRevenue</t>
-        </is>
-      </c>
+          <t>Enrollment fees 9,13</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
@@ -20413,17 +20439,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K199" s="5" t="n">
-        <v>0.668822</v>
-      </c>
-      <c r="L199" s="5" t="n">
-        <v>0.590541</v>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M199" s="5" t="n">
-        <v>0.63729</v>
+        <v>2.511875</v>
       </c>
       <c r="N199" s="5" t="n">
-        <v>0.718998</v>
+        <v>2.072536</v>
       </c>
       <c r="O199" t="inlineStr">
         <is>
@@ -20444,14 +20474,10 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Gross profit</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>GrossProfit</t>
-        </is>
-      </c>
+          <t>Education 13</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -20482,17 +20508,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K200" s="5" t="n">
-        <v>3.700525</v>
-      </c>
-      <c r="L200" s="5" t="n">
-        <v>4.752224</v>
-      </c>
-      <c r="M200" s="5" t="n">
-        <v>5.272082</v>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N200" s="5" t="n">
-        <v>6.668345</v>
+        <v>0.013704</v>
       </c>
       <c r="O200" t="inlineStr">
         <is>
@@ -20508,19 +20540,15 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Salaries and wages 6</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>SalariesAndWages</t>
-        </is>
-      </c>
+          <t>Licensing fees 13</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -20561,11 +20589,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M201" s="5" t="n">
-        <v>4.794595</v>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N201" s="5" t="n">
-        <v>5.501875</v>
+        <v>1.69444</v>
       </c>
       <c r="O201" t="inlineStr">
         <is>
@@ -20581,12 +20611,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Stock based compensation 10,11</t>
+          <t>Other revenue 11(c), 13</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
@@ -20631,10 +20661,10 @@
         </is>
       </c>
       <c r="M202" s="5" t="n">
-        <v>0.550405</v>
+        <v>0.288146</v>
       </c>
       <c r="N202" s="5" t="n">
-        <v>0.306135</v>
+        <v>0.188327</v>
       </c>
       <c r="O202" t="inlineStr">
         <is>
@@ -20650,15 +20680,19 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Software and licensing fees 6</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr"/>
+          <t>Total revenue</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -20689,21 +20723,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K203" s="5" t="n">
+        <v>4.369347</v>
+      </c>
+      <c r="L203" s="5" t="n">
+        <v>5.342765</v>
       </c>
       <c r="M203" s="5" t="n">
-        <v>0.605387</v>
+        <v>5.909372</v>
       </c>
       <c r="N203" s="5" t="n">
-        <v>0.949254</v>
+        <v>7.387343</v>
       </c>
       <c r="O203" t="inlineStr">
         <is>
@@ -20719,17 +20749,17 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Cost of sales</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>CostOfRevenue</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -20737,32 +20767,42 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F204" s="5" t="n">
-        <v>0.00878</v>
-      </c>
-      <c r="G204" s="5" t="n">
-        <v>0.110195</v>
-      </c>
-      <c r="H204" s="5" t="n">
-        <v>0.029666</v>
-      </c>
-      <c r="I204" s="5" t="n">
-        <v>0.056516</v>
-      </c>
-      <c r="J204" s="5" t="n">
-        <v>0.017768</v>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K204" s="5" t="n">
-        <v>0.270028</v>
+        <v>0.668822</v>
       </c>
       <c r="L204" s="5" t="n">
-        <v>0.297032</v>
+        <v>0.590541</v>
       </c>
       <c r="M204" s="5" t="n">
-        <v>0.254326</v>
+        <v>0.63729</v>
       </c>
       <c r="N204" s="5" t="n">
-        <v>0.209043</v>
+        <v>0.718998</v>
       </c>
       <c r="O204" t="inlineStr">
         <is>
@@ -20778,17 +20818,17 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Office and general</t>
+          <t>Gross profit</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>GrossProfit</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -20821,21 +20861,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K205" s="5" t="n">
+        <v>3.700525</v>
+      </c>
+      <c r="L205" s="5" t="n">
+        <v>4.752224</v>
       </c>
       <c r="M205" s="5" t="n">
-        <v>1.148372</v>
+        <v>5.272082</v>
       </c>
       <c r="N205" s="5" t="n">
-        <v>1.030882</v>
+        <v>6.668345</v>
       </c>
       <c r="O205" t="inlineStr">
         <is>
@@ -20856,10 +20892,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Bad debts 14</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr"/>
+          <t>Salaries and wages 6</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>SalariesAndWages</t>
+        </is>
+      </c>
       <c r="E206" t="inlineStr">
         <is>
           <t>-</t>
@@ -20901,10 +20941,10 @@
         </is>
       </c>
       <c r="M206" s="5" t="n">
-        <v>0.267155</v>
+        <v>4.794595</v>
       </c>
       <c r="N206" s="5" t="n">
-        <v>0.138549</v>
+        <v>5.501875</v>
       </c>
       <c r="O206" t="inlineStr">
         <is>
@@ -20925,14 +20965,10 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Depreciation 5</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Stock based compensation 10,11</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -20974,10 +21010,10 @@
         </is>
       </c>
       <c r="M207" s="5" t="n">
-        <v>0.016303</v>
+        <v>0.550405</v>
       </c>
       <c r="N207" s="5" t="n">
-        <v>0.020869</v>
+        <v>0.306135</v>
       </c>
       <c r="O207" t="inlineStr">
         <is>
@@ -20998,14 +21034,10 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Amortization 6</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
+          <t>Software and licensing fees 6</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr">
         <is>
           <t>-</t>
@@ -21047,10 +21079,10 @@
         </is>
       </c>
       <c r="M208" s="5" t="n">
-        <v>0.202708</v>
+        <v>0.605387</v>
       </c>
       <c r="N208" s="5" t="n">
-        <v>0.235476</v>
+        <v>0.949254</v>
       </c>
       <c r="O208" t="inlineStr">
         <is>
@@ -21071,12 +21103,12 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Expenses total</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -21084,42 +21116,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F209" s="5" t="n">
+        <v>0.00878</v>
+      </c>
+      <c r="G209" s="5" t="n">
+        <v>0.110195</v>
+      </c>
+      <c r="H209" s="5" t="n">
+        <v>0.029666</v>
+      </c>
+      <c r="I209" s="5" t="n">
+        <v>0.056516</v>
+      </c>
+      <c r="J209" s="5" t="n">
+        <v>0.017768</v>
       </c>
       <c r="K209" s="5" t="n">
-        <v>5.596071</v>
+        <v>0.270028</v>
       </c>
       <c r="L209" s="5" t="n">
-        <v>16.305791</v>
+        <v>0.297032</v>
       </c>
       <c r="M209" s="5" t="n">
-        <v>7.839251</v>
+        <v>0.254326</v>
       </c>
       <c r="N209" s="5" t="n">
-        <v>8.392083</v>
+        <v>0.209043</v>
       </c>
       <c r="O209" t="inlineStr">
         <is>
@@ -21140,12 +21162,12 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Loss from operations</t>
+          <t>Office and general</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -21178,17 +21200,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K210" s="5" t="n">
-        <v>-1.895546</v>
-      </c>
-      <c r="L210" s="5" t="n">
-        <v>-11.553567</v>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M210" s="5" t="n">
-        <v>-2.567169</v>
+        <v>1.148372</v>
       </c>
       <c r="N210" s="5" t="n">
-        <v>-1.723738</v>
+        <v>1.030882</v>
       </c>
       <c r="O210" t="inlineStr">
         <is>
@@ -21204,12 +21230,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Accretion expense 8</t>
+          <t>Bad debts 14</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -21254,10 +21280,10 @@
         </is>
       </c>
       <c r="M211" s="5" t="n">
-        <v>0.133868</v>
+        <v>0.267155</v>
       </c>
       <c r="N211" s="5" t="n">
-        <v>0.116106</v>
+        <v>0.138549</v>
       </c>
       <c r="O211" t="inlineStr">
         <is>
@@ -21273,17 +21299,17 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Interest expense 8,12</t>
+          <t>Depreciation 5</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>InterestExpenseOperating</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -21327,10 +21353,10 @@
         </is>
       </c>
       <c r="M212" s="5" t="n">
-        <v>0.090696</v>
+        <v>0.016303</v>
       </c>
       <c r="N212" s="5" t="n">
-        <v>0.352728</v>
+        <v>0.020869</v>
       </c>
       <c r="O212" t="inlineStr">
         <is>
@@ -21346,15 +21372,19 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Provision for interest and penalties 14</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr"/>
+          <t>Amortization 6</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -21396,10 +21426,10 @@
         </is>
       </c>
       <c r="M213" s="5" t="n">
-        <v>0.693101</v>
+        <v>0.202708</v>
       </c>
       <c r="N213" s="5" t="n">
-        <v>0.08182</v>
+        <v>0.235476</v>
       </c>
       <c r="O213" t="inlineStr">
         <is>
@@ -21415,17 +21445,17 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Foreign exchange (gain) loss</t>
+          <t>Expenses total</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -21458,21 +21488,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K214" s="5" t="n">
+        <v>5.596071</v>
+      </c>
+      <c r="L214" s="5" t="n">
+        <v>16.305791</v>
       </c>
       <c r="M214" s="5" t="n">
-        <v>0.001918</v>
+        <v>7.839251</v>
       </c>
       <c r="N214" s="5" t="n">
-        <v>-0.001029</v>
+        <v>8.392083</v>
       </c>
       <c r="O214" t="inlineStr">
         <is>
@@ -21488,15 +21514,19 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Gain on repurchase of debentures 8</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr"/>
+          <t>Loss from operations</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -21527,23 +21557,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K215" s="5" t="n">
+        <v>-1.895546</v>
+      </c>
+      <c r="L215" s="5" t="n">
+        <v>-11.553567</v>
+      </c>
+      <c r="M215" s="5" t="n">
+        <v>-2.567169</v>
       </c>
       <c r="N215" s="5" t="n">
-        <v>-0.138566</v>
+        <v>-1.723738</v>
       </c>
       <c r="O215" t="inlineStr">
         <is>
@@ -21564,14 +21588,10 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Net loss</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Accretion expense 8</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr">
         <is>
           <t>-</t>
@@ -21602,17 +21622,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K216" s="5" t="n">
-        <v>-2.055275</v>
-      </c>
-      <c r="L216" s="5" t="n">
-        <v>-11.433317</v>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M216" s="5" t="n">
-        <v>-3.486752</v>
+        <v>0.133868</v>
       </c>
       <c r="N216" s="5" t="n">
-        <v>-2.134797</v>
+        <v>0.116106</v>
       </c>
       <c r="O216" t="inlineStr">
         <is>
@@ -21628,15 +21652,19 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Other Comprehensive loss</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Currency translation adjustment</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr"/>
+          <t>Interest expense 8,12</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>-</t>
@@ -21667,17 +21695,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K217" s="5" t="n">
-        <v>0.512437</v>
-      </c>
-      <c r="L217" s="5" t="n">
-        <v>-0.131465</v>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M217" s="5" t="n">
-        <v>-0.107041</v>
+        <v>0.090696</v>
       </c>
       <c r="N217" s="5" t="n">
-        <v>-0.153447</v>
+        <v>0.352728</v>
       </c>
       <c r="O217" t="inlineStr">
         <is>
@@ -21693,12 +21725,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Other Comprehensive loss</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Comprehensive loss</t>
+          <t>Provision for interest and penalties 14</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
@@ -21732,17 +21764,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K218" s="5" t="n">
-        <v>-1.542838</v>
-      </c>
-      <c r="L218" s="5" t="n">
-        <v>-11.564782</v>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M218" s="5" t="n">
-        <v>-3.593793</v>
+        <v>0.693101</v>
       </c>
       <c r="N218" s="5" t="n">
-        <v>-2.288244</v>
+        <v>0.08182</v>
       </c>
       <c r="O218" t="inlineStr">
         <is>
@@ -21758,17 +21794,17 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Other Comprehensive loss</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Loss per share - basic and diluted</t>
+          <t>Foreign exchange (gain) loss</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -21801,17 +21837,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K219" s="5" t="n">
-        <v>-3e-08</v>
-      </c>
-      <c r="L219" s="5" t="n">
-        <v>-1.7e-07</v>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M219" s="5" t="n">
-        <v>-5e-08</v>
+        <v>0.001918</v>
       </c>
       <c r="N219" s="5" t="n">
-        <v>-3e-08</v>
+        <v>-0.001029</v>
       </c>
       <c r="O219" t="inlineStr">
         <is>
@@ -21827,12 +21867,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>outstanding common shares - basic</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>outstanding common shares - basic and diluted</t>
+          <t>Gain on repurchase of debentures 8</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
@@ -21876,11 +21916,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M220" s="5" t="n">
-        <v>72.71988399999999</v>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N220" s="5" t="n">
-        <v>73.148651</v>
+        <v>-0.138566</v>
       </c>
       <c r="O220" t="inlineStr">
         <is>
@@ -21896,15 +21938,19 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>#                      $                      $                      $                      $                      $</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr"/>
+          <t>Net loss</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
@@ -21935,21 +21981,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K221" s="5" t="n">
+        <v>-2.055275</v>
+      </c>
+      <c r="L221" s="5" t="n">
+        <v>-11.433317</v>
       </c>
       <c r="M221" s="5" t="n">
-        <v>-4.133983</v>
+        <v>-3.486752</v>
       </c>
       <c r="N221" s="5" t="n">
-        <v>-19.491825</v>
+        <v>-2.134797</v>
       </c>
       <c r="O221" t="inlineStr">
         <is>
@@ -21965,12 +22007,12 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Other Comprehensive loss</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Balance, June</t>
+          <t>Currency translation adjustment</t>
         </is>
       </c>
       <c r="D222" t="inlineStr"/>
@@ -22004,21 +22046,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K222" s="5" t="n">
+        <v>0.512437</v>
+      </c>
+      <c r="L222" s="5" t="n">
+        <v>-0.131465</v>
       </c>
       <c r="M222" s="5" t="n">
-        <v>0.002022</v>
+        <v>-0.107041</v>
       </c>
       <c r="N222" s="5" t="n">
-        <v>3e-05</v>
+        <v>-0.153447</v>
       </c>
       <c r="O222" t="inlineStr">
         <is>
@@ -22034,12 +22072,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Other Comprehensive loss</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Stock-based compensation - - 550,405 -</t>
+          <t>Comprehensive loss</t>
         </is>
       </c>
       <c r="D223" t="inlineStr"/>
@@ -22073,23 +22111,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K223" s="5" t="n">
+        <v>-1.542838</v>
+      </c>
+      <c r="L223" s="5" t="n">
+        <v>-11.564782</v>
       </c>
       <c r="M223" s="5" t="n">
-        <v>0.550405</v>
-      </c>
-      <c r="N223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3.593793</v>
+      </c>
+      <c r="N223" s="5" t="n">
+        <v>-2.288244</v>
       </c>
       <c r="O223" t="inlineStr">
         <is>
@@ -22105,15 +22137,19 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Other Comprehensive loss</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Warrants issued with convertible debentures - - 2,896 -</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr"/>
+          <t>Loss per share - basic and diluted</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>-</t>
@@ -22144,23 +22180,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K224" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="L224" s="5" t="n">
+        <v>-1.7e-07</v>
       </c>
       <c r="M224" s="5" t="n">
-        <v>0.002896</v>
-      </c>
-      <c r="N224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-5e-08</v>
+      </c>
+      <c r="N224" s="5" t="n">
+        <v>-3e-08</v>
       </c>
       <c r="O224" t="inlineStr">
         <is>
@@ -22176,12 +22206,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>outstanding common shares - basic</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Issuance of debentures - - 905,409 -</t>
+          <t>outstanding common shares - basic and diluted</t>
         </is>
       </c>
       <c r="D225" t="inlineStr"/>
@@ -22226,12 +22256,10 @@
         </is>
       </c>
       <c r="M225" s="5" t="n">
-        <v>0.905409</v>
-      </c>
-      <c r="N225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>72.71988399999999</v>
+      </c>
+      <c r="N225" s="5" t="n">
+        <v>73.148651</v>
       </c>
       <c r="O225" t="inlineStr">
         <is>
@@ -22252,7 +22280,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Conversion of debt (Note 9) 2,000,000 240,081 - -</t>
+          <t>#                      $                      $                      $                      $                      $</t>
         </is>
       </c>
       <c r="D226" t="inlineStr"/>
@@ -22297,12 +22325,10 @@
         </is>
       </c>
       <c r="M226" s="5" t="n">
-        <v>0.240081</v>
-      </c>
-      <c r="N226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4.133983</v>
+      </c>
+      <c r="N226" s="5" t="n">
+        <v>-19.491825</v>
       </c>
       <c r="O226" t="inlineStr">
         <is>
@@ -22323,7 +22349,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Exercise of warrants 100,000 42,288 (34,788) -</t>
+          <t>Balance, June</t>
         </is>
       </c>
       <c r="D227" t="inlineStr"/>
@@ -22368,12 +22394,10 @@
         </is>
       </c>
       <c r="M227" s="5" t="n">
-        <v>0.0075</v>
-      </c>
-      <c r="N227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002022</v>
+      </c>
+      <c r="N227" s="5" t="n">
+        <v>3e-05</v>
       </c>
       <c r="O227" t="inlineStr">
         <is>
@@ -22394,7 +22418,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Currency translation adjustment - - - (107,041)</t>
+          <t>Stock-based compensation - - 550,405 -</t>
         </is>
       </c>
       <c r="D228" t="inlineStr"/>
@@ -22439,7 +22463,7 @@
         </is>
       </c>
       <c r="M228" s="5" t="n">
-        <v>-0.107041</v>
+        <v>0.550405</v>
       </c>
       <c r="N228" t="inlineStr">
         <is>
@@ -22465,14 +22489,10 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Net loss for the year - - - -</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Warrants issued with convertible debentures - - 2,896 -</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr">
         <is>
           <t>-</t>
@@ -22514,10 +22534,12 @@
         </is>
       </c>
       <c r="M229" s="5" t="n">
-        <v>-3.486752</v>
-      </c>
-      <c r="N229" s="5" t="n">
-        <v>-3.486752</v>
+        <v>0.002896</v>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O229" t="inlineStr">
         <is>
@@ -22538,7 +22560,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Balance, June 30, 2023 73,148,651 8,438,709 8,402,921 115,462</t>
+          <t>Issuance of debentures - - 905,409 -</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
@@ -22583,10 +22605,12 @@
         </is>
       </c>
       <c r="M230" s="5" t="n">
-        <v>-6.021485</v>
-      </c>
-      <c r="N230" s="5" t="n">
-        <v>-22.978577</v>
+        <v>0.905409</v>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O230" t="inlineStr">
         <is>
@@ -22607,7 +22631,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Stock-based compensation - - 306,135 -</t>
+          <t>Conversion of debt (Note 9) 2,000,000 240,081 - -</t>
         </is>
       </c>
       <c r="D231" t="inlineStr"/>
@@ -22652,7 +22676,7 @@
         </is>
       </c>
       <c r="M231" s="5" t="n">
-        <v>0.306135</v>
+        <v>0.240081</v>
       </c>
       <c r="N231" t="inlineStr">
         <is>
@@ -22678,7 +22702,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Issuance of debentures - - 154,098 -</t>
+          <t>Exercise of warrants 100,000 42,288 (34,788) -</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
@@ -22723,7 +22747,7 @@
         </is>
       </c>
       <c r="M232" s="5" t="n">
-        <v>0.154098</v>
+        <v>0.0075</v>
       </c>
       <c r="N232" t="inlineStr">
         <is>
@@ -22749,7 +22773,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Debenture repurchase - - (20,958) -</t>
+          <t>Currency translation adjustment - - - (107,041)</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -22794,7 +22818,7 @@
         </is>
       </c>
       <c r="M233" s="5" t="n">
-        <v>-0.020958</v>
+        <v>-0.107041</v>
       </c>
       <c r="N233" t="inlineStr">
         <is>
@@ -22820,10 +22844,14 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Currency translation adjustment - - - (153,447)</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
+          <t>Net loss for the year - - - -</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>
@@ -22865,12 +22893,10 @@
         </is>
       </c>
       <c r="M234" s="5" t="n">
-        <v>-0.153447</v>
-      </c>
-      <c r="N234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3.486752</v>
+      </c>
+      <c r="N234" s="5" t="n">
+        <v>-3.486752</v>
       </c>
       <c r="O234" t="inlineStr">
         <is>
@@ -22891,7 +22917,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Balance, June 30, 2024 73,148,651 8,438,709 8,842,196 (37,985)</t>
+          <t>Balance, June 30, 2023 73,148,651 8,438,709 8,402,921 115,462</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -22936,10 +22962,10 @@
         </is>
       </c>
       <c r="M235" s="5" t="n">
-        <v>-7.870454</v>
+        <v>-6.021485</v>
       </c>
       <c r="N235" s="5" t="n">
-        <v>-25.113374</v>
+        <v>-22.978577</v>
       </c>
       <c r="O235" t="inlineStr">
         <is>
@@ -22955,12 +22981,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>June 30, 2022 June</t>
+          <t>Stock-based compensation - - 306,135 -</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -22994,16 +23020,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K236" s="5" t="n">
-        <v>0.002021</v>
-      </c>
-      <c r="L236" s="5" t="n">
-        <v>3e-05</v>
-      </c>
-      <c r="M236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M236" s="5" t="n">
+        <v>0.306135</v>
       </c>
       <c r="N236" t="inlineStr">
         <is>
@@ -23024,12 +23052,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Bank processing fees</t>
+          <t>Issuance of debentures - - 154,098 -</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -23063,16 +23091,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K237" s="5" t="n">
-        <v>2.555662</v>
-      </c>
-      <c r="L237" s="5" t="n">
-        <v>2.677973</v>
-      </c>
-      <c r="M237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M237" s="5" t="n">
+        <v>0.154098</v>
       </c>
       <c r="N237" t="inlineStr">
         <is>
@@ -23093,12 +23123,12 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Enrollment fees 10</t>
+          <t>Debenture repurchase - - (20,958) -</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
@@ -23132,16 +23162,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K238" s="5" t="n">
-        <v>1.573128</v>
-      </c>
-      <c r="L238" s="5" t="n">
-        <v>2.31652</v>
-      </c>
-      <c r="M238" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M238" s="5" t="n">
+        <v>-0.020958</v>
       </c>
       <c r="N238" t="inlineStr">
         <is>
@@ -23162,12 +23194,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Other revenue 12(d)</t>
+          <t>Currency translation adjustment - - - (153,447)</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -23201,16 +23233,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K239" s="5" t="n">
-        <v>0.240557</v>
-      </c>
-      <c r="L239" s="5" t="n">
-        <v>0.348272</v>
-      </c>
-      <c r="M239" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M239" s="5" t="n">
+        <v>-0.153447</v>
       </c>
       <c r="N239" t="inlineStr">
         <is>
@@ -23231,19 +23265,15 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Salaries and wages 7, 13</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>SalariesAndWages</t>
-        </is>
-      </c>
+          <t>Balance, June 30, 2024 73,148,651 8,438,709 8,842,196 (37,985)</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
@@ -23274,21 +23304,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K240" s="5" t="n">
-        <v>2.605533</v>
-      </c>
-      <c r="L240" s="5" t="n">
-        <v>5.386428</v>
-      </c>
-      <c r="M240" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N240" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M240" s="5" t="n">
+        <v>-7.870454</v>
+      </c>
+      <c r="N240" s="5" t="n">
+        <v>-25.113374</v>
       </c>
       <c r="O240" t="inlineStr">
         <is>
@@ -23304,12 +23334,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Note</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Management fees 12(b)</t>
+          <t>June 30, 2022 June</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -23344,12 +23374,10 @@
         </is>
       </c>
       <c r="K241" s="5" t="n">
-        <v>0.880285</v>
-      </c>
-      <c r="L241" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002021</v>
+      </c>
+      <c r="L241" s="5" t="n">
+        <v>3e-05</v>
       </c>
       <c r="M241" t="inlineStr">
         <is>
@@ -23375,12 +23403,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Stock based compensation 11,12</t>
+          <t>Bank processing fees</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -23415,10 +23443,10 @@
         </is>
       </c>
       <c r="K242" s="5" t="n">
-        <v>0.677295</v>
+        <v>2.555662</v>
       </c>
       <c r="L242" s="5" t="n">
-        <v>5.428928</v>
+        <v>2.677973</v>
       </c>
       <c r="M242" t="inlineStr">
         <is>
@@ -23444,12 +23472,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Software and licensing fees 7</t>
+          <t>Enrollment fees 10</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -23484,10 +23512,10 @@
         </is>
       </c>
       <c r="K243" s="5" t="n">
-        <v>0.584257</v>
+        <v>1.573128</v>
       </c>
       <c r="L243" s="5" t="n">
-        <v>0.685117</v>
+        <v>2.31652</v>
       </c>
       <c r="M243" t="inlineStr">
         <is>
@@ -23513,19 +23541,15 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Office and general 13</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Other revenue 12(d)</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
@@ -23557,10 +23581,10 @@
         </is>
       </c>
       <c r="K244" s="5" t="n">
-        <v>0.257238</v>
+        <v>0.240557</v>
       </c>
       <c r="L244" s="5" t="n">
-        <v>1.422213</v>
+        <v>0.348272</v>
       </c>
       <c r="M244" t="inlineStr">
         <is>
@@ -23591,10 +23615,14 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Listing expense 4</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr"/>
+          <t>Salaries and wages 7, 13</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>SalariesAndWages</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -23625,13 +23653,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K245" s="5" t="n">
+        <v>2.605533</v>
       </c>
       <c r="L245" s="5" t="n">
-        <v>1.397527</v>
+        <v>5.386428</v>
       </c>
       <c r="M245" t="inlineStr">
         <is>
@@ -23662,7 +23688,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Transaction costs 4</t>
+          <t>Management fees 12(b)</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
@@ -23696,13 +23722,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L246" s="5" t="n">
-        <v>1.275048</v>
+      <c r="K246" s="5" t="n">
+        <v>0.880285</v>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M246" t="inlineStr">
         <is>
@@ -23733,7 +23759,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Bad debts</t>
+          <t>Stock based compensation 11,12</t>
         </is>
       </c>
       <c r="D247" t="inlineStr"/>
@@ -23768,10 +23794,10 @@
         </is>
       </c>
       <c r="K247" s="5" t="n">
-        <v>0.170218</v>
+        <v>0.677295</v>
       </c>
       <c r="L247" s="5" t="n">
-        <v>0.254925</v>
+        <v>5.428928</v>
       </c>
       <c r="M247" t="inlineStr">
         <is>
@@ -23802,14 +23828,10 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Depreciation 6</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Software and licensing fees 7</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
@@ -23841,10 +23863,10 @@
         </is>
       </c>
       <c r="K248" s="5" t="n">
-        <v>0.000878</v>
+        <v>0.584257</v>
       </c>
       <c r="L248" s="5" t="n">
-        <v>0.006555</v>
+        <v>0.685117</v>
       </c>
       <c r="M248" t="inlineStr">
         <is>
@@ -23875,12 +23897,12 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Amortization 7</t>
+          <t>Office and general 13</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -23914,10 +23936,10 @@
         </is>
       </c>
       <c r="K249" s="5" t="n">
-        <v>0.150339</v>
+        <v>0.257238</v>
       </c>
       <c r="L249" s="5" t="n">
-        <v>0.152018</v>
+        <v>1.422213</v>
       </c>
       <c r="M249" t="inlineStr">
         <is>
@@ -23943,12 +23965,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Accretion expense 9</t>
+          <t>Listing expense 4</t>
         </is>
       </c>
       <c r="D250" t="inlineStr"/>
@@ -23982,11 +24004,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K250" s="5" t="n">
-        <v>0.100313</v>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L250" s="5" t="n">
-        <v>0.0226</v>
+        <v>1.397527</v>
       </c>
       <c r="M250" t="inlineStr">
         <is>
@@ -24012,19 +24036,15 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Interest expense</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>InterestExpenseOperating</t>
-        </is>
-      </c>
+          <t>Transaction costs 4</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr"/>
       <c r="E251" t="inlineStr">
         <is>
           <t>-</t>
@@ -24055,11 +24075,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K251" s="5" t="n">
-        <v>0.061863</v>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L251" s="5" t="n">
-        <v>0.019112</v>
+        <v>1.275048</v>
       </c>
       <c r="M251" t="inlineStr">
         <is>
@@ -24085,19 +24107,15 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Bad debts</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr"/>
       <c r="E252" t="inlineStr">
         <is>
           <t>-</t>
@@ -24129,10 +24147,10 @@
         </is>
       </c>
       <c r="K252" s="5" t="n">
-        <v>0.008711</v>
+        <v>0.170218</v>
       </c>
       <c r="L252" s="5" t="n">
-        <v>-0.012547</v>
+        <v>0.254925</v>
       </c>
       <c r="M252" t="inlineStr">
         <is>
@@ -24158,15 +24176,19 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Gain on debt modification 9</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr"/>
+          <t>Depreciation 6</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
           <t>-</t>
@@ -24198,10 +24220,10 @@
         </is>
       </c>
       <c r="K253" s="5" t="n">
-        <v>0.002276</v>
+        <v>0.000878</v>
       </c>
       <c r="L253" s="5" t="n">
-        <v>-0.001097</v>
+        <v>0.006555</v>
       </c>
       <c r="M253" t="inlineStr">
         <is>
@@ -24227,15 +24249,19 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Gain on derivative liabilities 14</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr"/>
+          <t>Amortization 7</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E254" t="inlineStr">
         <is>
           <t>-</t>
@@ -24267,10 +24293,10 @@
         </is>
       </c>
       <c r="K254" s="5" t="n">
-        <v>-0.013434</v>
+        <v>0.150339</v>
       </c>
       <c r="L254" s="5" t="n">
-        <v>-0.148318</v>
+        <v>0.152018</v>
       </c>
       <c r="M254" t="inlineStr">
         <is>
@@ -24296,12 +24322,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>common shares - basic and diluted</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>common shares - basic and diluted total</t>
+          <t>Accretion expense 9</t>
         </is>
       </c>
       <c r="D255" t="inlineStr"/>
@@ -24336,10 +24362,10 @@
         </is>
       </c>
       <c r="K255" s="5" t="n">
-        <v>60.435449</v>
+        <v>0.100313</v>
       </c>
       <c r="L255" s="5" t="n">
-        <v>68.05435799999999</v>
+        <v>0.0226</v>
       </c>
       <c r="M255" t="inlineStr">
         <is>
@@ -24365,15 +24391,19 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr"/>
+          <t>Interest expense</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -24405,10 +24435,10 @@
         </is>
       </c>
       <c r="K256" s="5" t="n">
-        <v>-4.133983</v>
+        <v>0.061863</v>
       </c>
       <c r="L256" s="5" t="n">
-        <v>-11.433317</v>
+        <v>0.019112</v>
       </c>
       <c r="M256" t="inlineStr">
         <is>
@@ -24434,15 +24464,19 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>$                                                                                                                             Deficiency                                                                                                                                                   Shareholder's</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>$                                                                                                                             Deficiency                                                                                                                                                   Shareholder's</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr"/>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E257" t="inlineStr">
         <is>
           <t>-</t>
@@ -24473,15 +24507,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L257" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K257" s="5" t="n">
+        <v>0.008711</v>
+      </c>
+      <c r="L257" s="5" t="n">
+        <v>-0.012547</v>
       </c>
       <c r="M257" t="inlineStr">
         <is>
@@ -24507,12 +24537,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>$                                                                                                                             Deficiency                                                                                                                                                   Shareholder's</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>$                                                                                                                             Deficiency                                                                                                                                                   Shareholder's total</t>
+          <t>Gain on debt modification 9</t>
         </is>
       </c>
       <c r="D258" t="inlineStr"/>
@@ -24547,10 +24577,10 @@
         </is>
       </c>
       <c r="K258" s="5" t="n">
-        <v>-19.491825</v>
+        <v>0.002276</v>
       </c>
       <c r="L258" s="5" t="n">
-        <v>-11.433317</v>
+        <v>-0.001097</v>
       </c>
       <c r="M258" t="inlineStr">
         <is>
@@ -24576,12 +24606,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>$                                                                                                                                                                   Comprehensive                                                                                                                             Accumulated        Income                                                                                                                                                                                                                                                                                                    financial                                                               Other</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>$                                                                                                                                                                   Comprehensive                                                                                                                             Accumulated        Income                                                                                                                                                                                                                                                                                                    financial                                                               Other</t>
+          <t>Gain on derivative liabilities 14</t>
         </is>
       </c>
       <c r="D259" t="inlineStr"/>
@@ -24615,15 +24645,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L259" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K259" s="5" t="n">
+        <v>-0.013434</v>
+      </c>
+      <c r="L259" s="5" t="n">
+        <v>-0.148318</v>
       </c>
       <c r="M259" t="inlineStr">
         <is>
@@ -24649,12 +24675,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>common shares - basic and diluted</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>common shares - basic and diluted total</t>
         </is>
       </c>
       <c r="D260" t="inlineStr"/>
@@ -24688,15 +24714,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L260" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K260" s="5" t="n">
+        <v>60.435449</v>
+      </c>
+      <c r="L260" s="5" t="n">
+        <v>68.05435799999999</v>
       </c>
       <c r="M260" t="inlineStr">
         <is>
@@ -24722,12 +24744,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>850,000 766,583 262,500 Shareholder’s of 4,306,293 2,121,875 1,298,900 3,142,500 Corp.) Shares 11) 58,300,000 62,606,293</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D261" t="inlineStr"/>
@@ -24762,10 +24784,10 @@
         </is>
       </c>
       <c r="K261" s="5" t="n">
-        <v>71.04865100000001</v>
+        <v>-4.133983</v>
       </c>
       <c r="L261" s="5" t="n">
-        <v>62.606293</v>
+        <v>-11.433317</v>
       </c>
       <c r="M261" t="inlineStr">
         <is>
@@ -24791,12 +24813,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>$                                                                                                                             Deficiency                                                                                                                                                   Shareholder's</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Transfer, filing and listing fees</t>
+          <t>$                                                                                                                             Deficiency                                                                                                                                                   Shareholder's</t>
         </is>
       </c>
       <c r="D262" t="inlineStr"/>
@@ -24805,23 +24827,35 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F262" s="5" t="n">
-        <v>0.0025</v>
-      </c>
-      <c r="G262" s="5" t="n">
-        <v>0.017937</v>
-      </c>
-      <c r="H262" s="5" t="n">
-        <v>0.028746</v>
-      </c>
-      <c r="I262" s="5" t="n">
-        <v>0.039106</v>
-      </c>
-      <c r="J262" s="5" t="n">
-        <v>0.017354</v>
-      </c>
-      <c r="K262" s="5" t="n">
-        <v>0.019801</v>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L262" t="inlineStr">
         <is>
@@ -24852,19 +24886,15 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>$                                                                                                                             Deficiency                                                                                                                                                   Shareholder's</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Consulting fees</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>$                                                                                                                             Deficiency                                                                                                                                                   Shareholder's total</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr"/>
       <c r="E263" t="inlineStr">
         <is>
           <t>-</t>
@@ -24875,25 +24905,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G263" s="5" t="n">
-        <v>0.067625</v>
-      </c>
-      <c r="H263" s="5" t="n">
-        <v>0.033828</v>
-      </c>
-      <c r="I263" s="5" t="n">
-        <v>0.010403</v>
-      </c>
-      <c r="J263" s="5" t="n">
-        <v>0.003933</v>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K263" s="5" t="n">
-        <v>0.004192</v>
-      </c>
-      <c r="L263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-19.491825</v>
+      </c>
+      <c r="L263" s="5" t="n">
+        <v>-11.433317</v>
       </c>
       <c r="M263" t="inlineStr">
         <is>
@@ -24919,19 +24955,15 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>$                                                                                                                                                                   Comprehensive                                                                                                                             Accumulated        Income                                                                                                                                                                                                                                                                                                    financial                                                               Other</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>$                                                                                                                                                                   Comprehensive                                                                                                                             Accumulated        Income                                                                                                                                                                                                                                                                                                    financial                                                               Other</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr"/>
       <c r="E264" t="inlineStr">
         <is>
           <t>-</t>
@@ -24942,20 +24974,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G264" s="5" t="n">
-        <v>0.004353</v>
-      </c>
-      <c r="H264" s="5" t="n">
-        <v>0.002763</v>
-      </c>
-      <c r="I264" s="5" t="n">
-        <v>0.001144</v>
-      </c>
-      <c r="J264" s="5" t="n">
-        <v>0.00179</v>
-      </c>
-      <c r="K264" s="5" t="n">
-        <v>0.001866</v>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L264" t="inlineStr">
         <is>
@@ -24986,19 +25028,15 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr"/>
       <c r="E265" t="inlineStr">
         <is>
           <t>-</t>
@@ -25024,11 +25062,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J265" s="5" t="n">
-        <v>-0.040845</v>
-      </c>
-      <c r="K265" s="5" t="n">
-        <v>-0.096119</v>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L265" t="inlineStr">
         <is>
@@ -25059,12 +25101,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding during the year</t>
+          <t>850,000 766,583 262,500 Shareholder’s of 4,306,293 2,121,875 1,298,900 3,142,500 Corp.) Shares 11) 58,300,000 62,606,293</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
@@ -25093,16 +25135,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J266" s="5" t="n">
-        <v>3.85</v>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K266" s="5" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="L266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>71.04865100000001</v>
+      </c>
+      <c r="L266" s="5" t="n">
+        <v>62.606293</v>
       </c>
       <c r="M266" t="inlineStr">
         <is>
@@ -25133,44 +25175,32 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Transfer, filing and listing fees</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr"/>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F267" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H267" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I267" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F267" s="5" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="G267" s="5" t="n">
+        <v>0.017937</v>
+      </c>
+      <c r="H267" s="5" t="n">
+        <v>0.028746</v>
+      </c>
+      <c r="I267" s="5" t="n">
+        <v>0.039106</v>
       </c>
       <c r="J267" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.017354</v>
       </c>
       <c r="K267" s="5" t="n">
-        <v>-2e-08</v>
+        <v>0.019801</v>
       </c>
       <c r="L267" t="inlineStr">
         <is>
@@ -25206,7 +25236,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Consulting fees</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -25225,23 +25255,19 @@
         </is>
       </c>
       <c r="G268" s="5" t="n">
-        <v>0.017569</v>
+        <v>0.067625</v>
       </c>
       <c r="H268" s="5" t="n">
-        <v>0.001537</v>
+        <v>0.033828</v>
       </c>
       <c r="I268" s="5" t="n">
-        <v>0.000779</v>
-      </c>
-      <c r="J268" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K268" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.010403</v>
+      </c>
+      <c r="J268" s="5" t="n">
+        <v>0.003933</v>
+      </c>
+      <c r="K268" s="5" t="n">
+        <v>0.004192</v>
       </c>
       <c r="L268" t="inlineStr">
         <is>
@@ -25277,12 +25303,12 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year</t>
+          <t>Office</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -25290,25 +25316,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F269" s="5" t="n">
-        <v>-0.01128</v>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G269" s="5" t="n">
-        <v>-0.362493</v>
+        <v>0.004353</v>
       </c>
       <c r="H269" s="5" t="n">
-        <v>-0.018839</v>
+        <v>0.002763</v>
       </c>
       <c r="I269" s="5" t="n">
-        <v>-0.107948</v>
+        <v>0.001144</v>
       </c>
       <c r="J269" s="5" t="n">
-        <v>-0.040845</v>
-      </c>
-      <c r="K269" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.00179</v>
+      </c>
+      <c r="K269" s="5" t="n">
+        <v>0.001866</v>
       </c>
       <c r="L269" t="inlineStr">
         <is>
@@ -25339,39 +25365,49 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding during the</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding during the year</t>
-        </is>
-      </c>
-      <c r="D270" t="inlineStr"/>
+          <t>Net loss and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F270" s="5" t="n">
-        <v>7.017995</v>
-      </c>
-      <c r="G270" s="5" t="n">
-        <v>4.651844</v>
-      </c>
-      <c r="H270" s="5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I270" s="5" t="n">
-        <v>3.783836</v>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J270" s="5" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.040845</v>
+      </c>
+      <c r="K270" s="5" t="n">
+        <v>-0.096119</v>
       </c>
       <c r="L270" t="inlineStr">
         <is>
@@ -25402,43 +25438,45 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding during the</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Weighted average number of shares outstanding during the year</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr"/>
       <c r="E271" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F271" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="G271" s="5" t="n">
-        <v>-8e-08</v>
-      </c>
-      <c r="H271" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="I271" s="5" t="n">
-        <v>-3e-08</v>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J271" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="K271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.85</v>
+      </c>
+      <c r="K271" s="5" t="n">
+        <v>3.85</v>
       </c>
       <c r="L271" t="inlineStr">
         <is>
@@ -25474,40 +25512,42 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Rent and parking</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr"/>
+          <t>Basic and diluted loss per share</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E272" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G272" s="5" t="n">
-        <v>0.016401</v>
-      </c>
-      <c r="H272" s="5" t="n">
-        <v>0.00172</v>
+      <c r="F272" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J272" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="K272" s="5" t="n">
+        <v>-2e-08</v>
       </c>
       <c r="L272" t="inlineStr">
         <is>
@@ -25543,10 +25583,14 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Meals and entertainment</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr"/>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
@@ -25558,15 +25602,13 @@
         </is>
       </c>
       <c r="G273" s="5" t="n">
-        <v>0.011141</v>
+        <v>0.017569</v>
       </c>
       <c r="H273" s="5" t="n">
-        <v>0.001091</v>
-      </c>
-      <c r="I273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.001537</v>
+      </c>
+      <c r="I273" s="5" t="n">
+        <v>0.000779</v>
       </c>
       <c r="J273" t="inlineStr">
         <is>
@@ -25612,37 +25654,33 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Recovery of expenses (note 9)</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr"/>
+          <t>Loss and comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F274" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F274" s="5" t="n">
+        <v>-0.01128</v>
+      </c>
+      <c r="G274" s="5" t="n">
+        <v>-0.362493</v>
       </c>
       <c r="H274" s="5" t="n">
-        <v>-0.080512</v>
-      </c>
-      <c r="I274" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J274" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.018839</v>
+      </c>
+      <c r="I274" s="5" t="n">
+        <v>-0.107948</v>
+      </c>
+      <c r="J274" s="5" t="n">
+        <v>-0.040845</v>
       </c>
       <c r="K274" t="inlineStr">
         <is>
@@ -25678,12 +25716,12 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number of shares outstanding during the</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Stock based compensation</t>
+          <t>Weighted average number of shares outstanding during the year</t>
         </is>
       </c>
       <c r="D275" t="inlineStr"/>
@@ -25692,28 +25730,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F275" s="5" t="n">
+        <v>7.017995</v>
       </c>
       <c r="G275" s="5" t="n">
-        <v>0.1145</v>
-      </c>
-      <c r="H275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.651844</v>
+      </c>
+      <c r="H275" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I275" s="5" t="n">
+        <v>3.783836</v>
+      </c>
+      <c r="J275" s="5" t="n">
+        <v>3.85</v>
       </c>
       <c r="K275" t="inlineStr">
         <is>
@@ -25749,17 +25779,17 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number of shares outstanding during the</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Marketing and promotion</t>
+          <t>Basic and diluted loss per share</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -25767,28 +25797,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F276" s="5" t="n">
+        <v>-2e-08</v>
       </c>
       <c r="G276" s="5" t="n">
-        <v>0.001762</v>
-      </c>
-      <c r="H276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-8e-08</v>
+      </c>
+      <c r="H276" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="I276" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="J276" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="K276" t="inlineStr">
         <is>
@@ -25829,7 +25851,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Conferences</t>
+          <t>Rent and parking</t>
         </is>
       </c>
       <c r="D277" t="inlineStr"/>
@@ -25844,12 +25866,10 @@
         </is>
       </c>
       <c r="G277" s="5" t="n">
-        <v>0.00101</v>
-      </c>
-      <c r="H277" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.016401</v>
+      </c>
+      <c r="H277" s="5" t="n">
+        <v>0.00172</v>
       </c>
       <c r="I277" t="inlineStr">
         <is>
@@ -25900,7 +25920,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Non-refundable deposit</t>
+          <t>Meals and entertainment</t>
         </is>
       </c>
       <c r="D278" t="inlineStr"/>
@@ -25915,12 +25935,10 @@
         </is>
       </c>
       <c r="G278" s="5" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="H278" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.011141</v>
+      </c>
+      <c r="H278" s="5" t="n">
+        <v>0.001091</v>
       </c>
       <c r="I278" t="inlineStr">
         <is>
@@ -25971,7 +25989,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Recovery of expenses (note 8)</t>
+          <t>Recovery of expenses (note 9)</t>
         </is>
       </c>
       <c r="D279" t="inlineStr"/>
@@ -25985,8 +26003,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G279" s="5" t="n">
-        <v>-0.025</v>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H279" s="5" t="n">
         <v>-0.080512</v>
@@ -26022,6 +26042,509 @@
         </is>
       </c>
       <c r="O279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Stock based compensation</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr"/>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G280" s="5" t="n">
+        <v>0.1145</v>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Marketing and promotion</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G281" s="5" t="n">
+        <v>0.001762</v>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Conferences</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr"/>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G282" s="5" t="n">
+        <v>0.00101</v>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Non-refundable deposit</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr"/>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G283" s="5" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Recovery of expenses (note 8)</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr"/>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G284" s="5" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="H284" s="5" t="n">
+        <v>-0.080512</v>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss for the period</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F285" s="5" t="n">
+        <v>-0.01128</v>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding during the period</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr"/>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F286" s="5" t="n">
+        <v>7.017995</v>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr">
         <is>
           <t>-</t>
         </is>
